--- a/папс/Банкомат/KostyaBank/comp.xlsx
+++ b/папс/Банкомат/KostyaBank/comp.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Номер карты</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>1111111111111111</t>
+  </si>
+  <si>
+    <t>Пин-код</t>
   </si>
 </sst>
 </file>
@@ -352,13 +355,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -368,8 +371,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -378,6 +384,9 @@
       </c>
       <c r="C2">
         <v>1052</v>
+      </c>
+      <c r="D2">
+        <v>1111</v>
       </c>
     </row>
   </sheetData>
